--- a/data/trans_orig/IP41-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP41-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71330</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64985</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>76633</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>64547</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57687</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71136</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57132</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>70377</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>74,41%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>71330</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>64780</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>76731</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125976</t>
+          <t>126940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143473</t>
+          <t>143925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15515</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10212</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21860</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22195</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15606</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29055</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16365</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29610</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15515</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10114</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22065</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30114</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>46647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>86742</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86742</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86742</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>441153</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>431786</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>448998</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>389094</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>380509</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>395675</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>380757</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>395341</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>94,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>441153</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>431575</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>448243</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>818420</t>
+          <t>817221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>840907</t>
+          <t>841402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30118</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22273</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39485</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22999</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16418</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31584</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16752</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>31336</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30118</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23028</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39696</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>41962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64944</t>
+          <t>66143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>471271</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>471271</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>471271</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>412093</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>412093</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>412093</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>471271</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>471271</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>471271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>148656</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>143202</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>152682</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>157832</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>150614</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>163271</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>151378</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>162931</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>91,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>148656</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>143063</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>152756</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>298235</t>
+          <t>298279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314019</t>
+          <t>314023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14323</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>14596</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9157</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21814</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9497</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21050</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8869</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4769</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14462</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>157525</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>157525</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>157525</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172428</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172428</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172428</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>157525</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>157525</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>157525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>648186</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>672164</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>597408</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>622663</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>598853</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>622097</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>648998</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>671824</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1255897</t>
+          <t>1255890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1287529</t>
+          <t>1289194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54502</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>43476</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>67454</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>59790</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48600</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>49166</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>72410</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>8,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>54502</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>43816</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>66642</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>97709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131006</t>
+          <t>131013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>715640</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>671263</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>671263</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>671263</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>715640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69586</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63324</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>74964</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>74819</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>67874</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80278</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>67459</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80180</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>81,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69586</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>62173</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>74686</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135509</t>
+          <t>134924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152766</t>
+          <t>152324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16606</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11228</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22868</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17550</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12091</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24495</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12189</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24910</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>19,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,09%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16606</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11506</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24019</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>26237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43052</t>
+          <t>43637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>437262</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>424522</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>448692</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>580</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>400135</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>388338</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>409805</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>387756</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>410292</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>88,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>437262</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>424978</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>448658</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>819335</t>
+          <t>821451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>852327</t>
+          <t>854588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45754</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69924</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>51357</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41687</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63154</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>41200</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63736</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>57184</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>45788</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>69468</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93610</t>
+          <t>91349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126602</t>
+          <t>124486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>451492</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>451492</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>451492</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>158384</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>151033</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>163576</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>158769</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>153005</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>162534</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>153382</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>162178</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>95,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>158384</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>151003</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>163773</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>308502</t>
+          <t>308590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>323877</t>
+          <t>324525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13844</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8652</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21195</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8043</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4278</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13807</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4634</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13430</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13844</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8455</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21225</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30539</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>649810</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>678994</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>912</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>620351</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>647122</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>619897</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>647022</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>648205</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>678540</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1279449</t>
+          <t>1281021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1317524</t>
+          <t>1317721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>87634</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73872</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103056</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76950</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63551</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90322</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>63651</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>90776</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>87634</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>74326</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>104661</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146015</t>
+          <t>145818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184090</t>
+          <t>182518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>710673</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>710673</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>710673</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46716</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40002</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52937</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>48390</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42995</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52715</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42898</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>52272</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>81,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46716</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40349</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>53357</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>86608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102699</t>
+          <t>102738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,27%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21898</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15677</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28612</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10988</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6663</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16383</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16480</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>18,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21898</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15257</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28265</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>41385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>407339</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>392257</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>419504</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>390480</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>376890</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>403368</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>376209</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>402780</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>407339</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>393815</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>421380</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>778414</t>
+          <t>779137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>816116</t>
+          <t>816426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80109</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67944</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95191</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>80909</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68021</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94499</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68609</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>95180</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>17,16%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80109</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>66068</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93633</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142722</t>
+          <t>142412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180424</t>
+          <t>179701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>487448</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>487448</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>487448</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>471389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>471389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>471389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>487448</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>487448</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>487448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>168714</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>160332</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>174555</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>153406</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>145646</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>159564</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>145828</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>160160</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>88,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>168714</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>160288</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>174593</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310459</t>
+          <t>310358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331021</t>
+          <t>331001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18781</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12940</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27163</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19297</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13139</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27057</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12543</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26875</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18781</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12902</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27207</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29176</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>49839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>605446</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>638865</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>81,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>592276</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>576591</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>607939</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>574859</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>607310</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>604626</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>638256</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1192569</t>
+          <t>1189699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1236573</t>
+          <t>1236418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>120788</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>104693</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>138112</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>111194</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95531</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>126879</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>96160</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>128611</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>15,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>120788</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>105302</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>138932</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,24%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210455</t>
+          <t>210610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254459</t>
+          <t>257329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>743558</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>703470</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>703470</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>703470</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>743558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
